--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9933,7 +9933,7 @@
         <v>275.39</v>
       </c>
       <c r="C317" t="n">
-        <v>272.58</v>
+        <v>276.99</v>
       </c>
       <c r="D317" t="n">
         <v>276.02</v>
@@ -9950,6 +9950,36 @@
       <c r="H317" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>271.97</v>
+      </c>
+      <c r="C318" t="n">
+        <v>274.41</v>
+      </c>
+      <c r="D318" t="n">
+        <v>276.03</v>
+      </c>
+      <c r="E318" t="n">
+        <v>283.9</v>
+      </c>
+      <c r="F318" t="n">
+        <v>272.94</v>
+      </c>
+      <c r="G318" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13187,6 +13217,16 @@
       </c>
       <c r="B322" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -13355,28 +13395,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6204177831053556</v>
+        <v>0.6253654134535619</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2561797457792481</v>
+        <v>0.2600654240437185</v>
       </c>
       <c r="M2" t="n">
-        <v>6.276840863747385</v>
+        <v>6.282534091133874</v>
       </c>
       <c r="N2" t="n">
-        <v>55.1217059644595</v>
+        <v>55.11150362836062</v>
       </c>
       <c r="O2" t="n">
-        <v>7.424399367252512</v>
+        <v>7.423712253876804</v>
       </c>
       <c r="P2" t="n">
-        <v>248.4725748606334</v>
+        <v>248.4188872501458</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13433,28 +13473,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4907189645905097</v>
+        <v>0.4980093094768231</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2182531579528926</v>
+        <v>0.2233552246127759</v>
       </c>
       <c r="M3" t="n">
-        <v>5.193824711137345</v>
+        <v>5.211148145694955</v>
       </c>
       <c r="N3" t="n">
-        <v>42.54046660096461</v>
+        <v>42.71349116142708</v>
       </c>
       <c r="O3" t="n">
-        <v>6.522305313381505</v>
+        <v>6.535555918315372</v>
       </c>
       <c r="P3" t="n">
-        <v>255.2675126717977</v>
+        <v>255.1884889803873</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13511,28 +13551,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5149831776214638</v>
+        <v>0.5135310984051326</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2248390596875585</v>
+        <v>0.2250864733782735</v>
       </c>
       <c r="M4" t="n">
-        <v>5.416174746742719</v>
+        <v>5.405902677345967</v>
       </c>
       <c r="N4" t="n">
-        <v>45.09591167329341</v>
+        <v>44.96775233692097</v>
       </c>
       <c r="O4" t="n">
-        <v>6.715348961393846</v>
+        <v>6.705799902839405</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6598923259135</v>
+        <v>264.6756490938765</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13589,28 +13629,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4872976034660071</v>
+        <v>0.4843517313034452</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239028428918892</v>
+        <v>0.2228307125543045</v>
       </c>
       <c r="M5" t="n">
-        <v>5.16433260610208</v>
+        <v>5.162058783573323</v>
       </c>
       <c r="N5" t="n">
-        <v>40.5953229872048</v>
+        <v>40.52528999571351</v>
       </c>
       <c r="O5" t="n">
-        <v>6.371445910247123</v>
+        <v>6.365947690306096</v>
       </c>
       <c r="P5" t="n">
-        <v>275.4421696295415</v>
+        <v>275.474135808516</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13667,28 +13707,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4528024977416339</v>
+        <v>0.4483936624167011</v>
       </c>
       <c r="J6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1478946644069582</v>
+        <v>0.1460860841558772</v>
       </c>
       <c r="M6" t="n">
-        <v>6.122856370132117</v>
+        <v>6.124339119422832</v>
       </c>
       <c r="N6" t="n">
-        <v>58.26253428045168</v>
+        <v>58.20871504020979</v>
       </c>
       <c r="O6" t="n">
-        <v>7.632989865082469</v>
+        <v>7.629463614187421</v>
       </c>
       <c r="P6" t="n">
-        <v>267.5269909413767</v>
+        <v>267.5748319919344</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13745,28 +13785,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07023598391922287</v>
+        <v>0.06795718151501022</v>
       </c>
       <c r="J7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008027003925686782</v>
+        <v>0.007565006071556857</v>
       </c>
       <c r="M7" t="n">
-        <v>4.42203744470385</v>
+        <v>4.418831856374905</v>
       </c>
       <c r="N7" t="n">
-        <v>30.06745579679322</v>
+        <v>30.00732922942911</v>
       </c>
       <c r="O7" t="n">
-        <v>5.483379961008832</v>
+        <v>5.477894598240195</v>
       </c>
       <c r="P7" t="n">
-        <v>329.1353752186656</v>
+        <v>329.1601029059109</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13804,7 +13844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27092,7 +27132,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>-35.53038206615793,174.46028206731236</t>
+          <t>-35.53038108289364,174.46033068577876</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -27118,6 +27158,48 @@
       <c r="H317" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.529619048368914,174.46029726716662</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.53038165813907,174.46030224232246</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.53122126938711,174.46038268098047</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.532131932881214,174.46080537592948</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-35.53289125111614,174.46143335220464</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-35.53307106069519,174.46251712905286</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9978,6 +9978,36 @@
         <v>327.64</v>
       </c>
       <c r="H318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>273.38</v>
+      </c>
+      <c r="C319" t="n">
+        <v>275.56</v>
+      </c>
+      <c r="D319" t="n">
+        <v>278.04</v>
+      </c>
+      <c r="E319" t="n">
+        <v>285.47</v>
+      </c>
+      <c r="F319" t="n">
+        <v>274.77</v>
+      </c>
+      <c r="G319" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="H319" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9994,7 +10024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13227,6 +13257,16 @@
       </c>
       <c r="B323" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -13395,28 +13435,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6253654134535619</v>
+        <v>0.6311790376391799</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2600654240437185</v>
+        <v>0.2642810828708327</v>
       </c>
       <c r="M2" t="n">
-        <v>6.282534091133874</v>
+        <v>6.292595429034318</v>
       </c>
       <c r="N2" t="n">
-        <v>55.11150362836062</v>
+        <v>55.16457232911948</v>
       </c>
       <c r="O2" t="n">
-        <v>7.423712253876804</v>
+        <v>7.427285663627021</v>
       </c>
       <c r="P2" t="n">
-        <v>248.4188872501458</v>
+        <v>248.3555851483812</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13473,28 +13513,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4980093094768231</v>
+        <v>0.5029753635732858</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2233552246127759</v>
+        <v>0.2274356849560235</v>
       </c>
       <c r="M3" t="n">
-        <v>5.211148145694955</v>
+        <v>5.217563704356364</v>
       </c>
       <c r="N3" t="n">
-        <v>42.71349116142708</v>
+        <v>42.7443522320191</v>
       </c>
       <c r="O3" t="n">
-        <v>6.535555918315372</v>
+        <v>6.537916505433448</v>
       </c>
       <c r="P3" t="n">
-        <v>255.1884889803873</v>
+        <v>255.1344157118467</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13551,28 +13591,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5135310984051326</v>
+        <v>0.5134370544460771</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2250864733782735</v>
+        <v>0.2263152555044284</v>
       </c>
       <c r="M4" t="n">
-        <v>5.405902677345967</v>
+        <v>5.389339541890728</v>
       </c>
       <c r="N4" t="n">
-        <v>44.96775233692097</v>
+        <v>44.82640354823799</v>
       </c>
       <c r="O4" t="n">
-        <v>6.705799902839405</v>
+        <v>6.695252314008636</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6756490938765</v>
+        <v>264.6766730988821</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13629,28 +13669,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4843517313034452</v>
+        <v>0.4824849598338167</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2228307125543045</v>
+        <v>0.2226745556269051</v>
       </c>
       <c r="M5" t="n">
-        <v>5.162058783573323</v>
+        <v>5.154604717742875</v>
       </c>
       <c r="N5" t="n">
-        <v>40.52528999571351</v>
+        <v>40.42119287004904</v>
       </c>
       <c r="O5" t="n">
-        <v>6.365947690306096</v>
+        <v>6.35776634283213</v>
       </c>
       <c r="P5" t="n">
-        <v>275.474135808516</v>
+        <v>275.4944622957069</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13707,28 +13747,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4483936624167011</v>
+        <v>0.4452650409220481</v>
       </c>
       <c r="J6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1460860841558772</v>
+        <v>0.1451239408717327</v>
       </c>
       <c r="M6" t="n">
-        <v>6.124339119422832</v>
+        <v>6.119666547659691</v>
       </c>
       <c r="N6" t="n">
-        <v>58.20871504020979</v>
+        <v>58.09122910859124</v>
       </c>
       <c r="O6" t="n">
-        <v>7.629463614187421</v>
+        <v>7.621760236886965</v>
       </c>
       <c r="P6" t="n">
-        <v>267.5748319919344</v>
+        <v>267.6088982318416</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13785,28 +13825,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06795718151501022</v>
+        <v>0.06570365065404908</v>
       </c>
       <c r="J7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007565006071556857</v>
+        <v>0.007119218731482135</v>
       </c>
       <c r="M7" t="n">
-        <v>4.418831856374905</v>
+        <v>4.415435416540621</v>
       </c>
       <c r="N7" t="n">
-        <v>30.00732922942911</v>
+        <v>29.94698090930282</v>
       </c>
       <c r="O7" t="n">
-        <v>5.477894598240195</v>
+        <v>5.472383476082686</v>
       </c>
       <c r="P7" t="n">
-        <v>329.1601029059109</v>
+        <v>329.1846406529918</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13844,7 +13884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27203,6 +27243,48 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.52961923585577,174.4603128147643</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.53038140173205,174.46031492060732</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.531218124649676,174.46040451103457</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.532125110366515,174.4608205457143</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-35.53287984251465,174.4614479298928</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-35.53307106069519,174.46251712905286</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10010,6 +10010,36 @@
       <c r="H319" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>275.07</v>
+      </c>
+      <c r="C320" t="n">
+        <v>279.54</v>
+      </c>
+      <c r="D320" t="n">
+        <v>281.02</v>
+      </c>
+      <c r="E320" t="n">
+        <v>289.11</v>
+      </c>
+      <c r="F320" t="n">
+        <v>280.3</v>
+      </c>
+      <c r="G320" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13267,6 +13297,16 @@
       </c>
       <c r="B324" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -13435,28 +13475,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6311790376391799</v>
+        <v>0.6380437704676647</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2642810828708327</v>
+        <v>0.2688914860827785</v>
       </c>
       <c r="M2" t="n">
-        <v>6.292595429034318</v>
+        <v>6.307729836998104</v>
       </c>
       <c r="N2" t="n">
-        <v>55.16457232911948</v>
+        <v>55.30160704345693</v>
       </c>
       <c r="O2" t="n">
-        <v>7.427285663627021</v>
+        <v>7.436505028806001</v>
       </c>
       <c r="P2" t="n">
-        <v>248.3555851483812</v>
+        <v>248.2802692763496</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13513,28 +13553,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5029753635732858</v>
+        <v>0.5105858642073394</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2274356849560235</v>
+        <v>0.2325181453124834</v>
       </c>
       <c r="M3" t="n">
-        <v>5.217563704356364</v>
+        <v>5.235375555392143</v>
       </c>
       <c r="N3" t="n">
-        <v>42.7443522320191</v>
+        <v>42.99132759464258</v>
       </c>
       <c r="O3" t="n">
-        <v>6.537916505433448</v>
+        <v>6.55677722624786</v>
       </c>
       <c r="P3" t="n">
-        <v>255.1344157118467</v>
+        <v>255.0509177074565</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13591,28 +13631,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5134370544460771</v>
+        <v>0.5153207665475509</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2263152555044284</v>
+        <v>0.2288411183401609</v>
       </c>
       <c r="M4" t="n">
-        <v>5.389339541890728</v>
+        <v>5.380891849492723</v>
       </c>
       <c r="N4" t="n">
-        <v>44.82640354823799</v>
+        <v>44.70922151759032</v>
       </c>
       <c r="O4" t="n">
-        <v>6.695252314008636</v>
+        <v>6.686495458578457</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6766730988821</v>
+        <v>264.6560061008905</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13669,28 +13709,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4824849598338167</v>
+        <v>0.483062859235615</v>
       </c>
       <c r="J5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2226745556269051</v>
+        <v>0.2243939972873923</v>
       </c>
       <c r="M5" t="n">
-        <v>5.154604717742875</v>
+        <v>5.14100913937801</v>
       </c>
       <c r="N5" t="n">
-        <v>40.42119287004904</v>
+        <v>40.29667735804318</v>
       </c>
       <c r="O5" t="n">
-        <v>6.35776634283213</v>
+        <v>6.347966395472111</v>
       </c>
       <c r="P5" t="n">
-        <v>275.4944622957069</v>
+        <v>275.4881219182326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13747,28 +13787,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4452650409220481</v>
+        <v>0.4458815076789751</v>
       </c>
       <c r="J6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1451239408717327</v>
+        <v>0.1464053289761236</v>
       </c>
       <c r="M6" t="n">
-        <v>6.119666547659691</v>
+        <v>6.103240963315248</v>
       </c>
       <c r="N6" t="n">
-        <v>58.09122910859124</v>
+        <v>57.91162461899088</v>
       </c>
       <c r="O6" t="n">
-        <v>7.621760236886965</v>
+        <v>7.60996876596684</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6088982318416</v>
+        <v>267.6021347156878</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13825,28 +13865,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06570365065404908</v>
+        <v>0.06344828236046397</v>
       </c>
       <c r="J7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007119218731482135</v>
+        <v>0.006684715470486768</v>
       </c>
       <c r="M7" t="n">
-        <v>4.415435416540621</v>
+        <v>4.411864978994238</v>
       </c>
       <c r="N7" t="n">
-        <v>29.94698090930282</v>
+        <v>29.88656118879335</v>
       </c>
       <c r="O7" t="n">
-        <v>5.472383476082686</v>
+        <v>5.466860267904544</v>
       </c>
       <c r="P7" t="n">
-        <v>329.1846406529918</v>
+        <v>329.2093852474324</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13884,7 +13924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27285,6 +27325,48 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.52961946057138,174.46033144982823</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.530380514330524,174.46035879849657</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-35.53121346229541,174.46043687598703</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-35.532109292554594,174.4608557164155</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-35.532845367331646,174.4614919815702</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-35.53307106069519,174.46251712905286</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10038,6 +10038,66 @@
         <v>327.64</v>
       </c>
       <c r="H320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>276.96</v>
+      </c>
+      <c r="C321" t="n">
+        <v>280.08</v>
+      </c>
+      <c r="D321" t="n">
+        <v>282.7</v>
+      </c>
+      <c r="E321" t="n">
+        <v>288.69</v>
+      </c>
+      <c r="F321" t="n">
+        <v>279.08</v>
+      </c>
+      <c r="G321" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>274.69</v>
+      </c>
+      <c r="C322" t="n">
+        <v>278.47</v>
+      </c>
+      <c r="D322" t="n">
+        <v>278.59</v>
+      </c>
+      <c r="E322" t="n">
+        <v>286.93</v>
+      </c>
+      <c r="F322" t="n">
+        <v>275.98</v>
+      </c>
+      <c r="G322" t="n">
+        <v>330.61</v>
+      </c>
+      <c r="H322" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10054,7 +10114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13307,6 +13367,26 @@
       </c>
       <c r="B325" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -13475,28 +13555,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6380437704676647</v>
+        <v>0.6524011035312958</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2688914860827785</v>
+        <v>0.2782591351608448</v>
       </c>
       <c r="M2" t="n">
-        <v>6.307729836998104</v>
+        <v>6.341855331123954</v>
       </c>
       <c r="N2" t="n">
-        <v>55.30160704345693</v>
+        <v>55.64755728537668</v>
       </c>
       <c r="O2" t="n">
-        <v>7.436505028806001</v>
+        <v>7.459729035653821</v>
       </c>
       <c r="P2" t="n">
-        <v>248.2802692763496</v>
+        <v>248.1221138461284</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13553,28 +13633,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5105858642073394</v>
+        <v>0.5250370519273552</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2325181453124834</v>
+        <v>0.2424401573084761</v>
       </c>
       <c r="M3" t="n">
-        <v>5.235375555392143</v>
+        <v>5.267502157235262</v>
       </c>
       <c r="N3" t="n">
-        <v>42.99132759464258</v>
+        <v>43.41873438817451</v>
       </c>
       <c r="O3" t="n">
-        <v>6.55677722624786</v>
+        <v>6.589289368981644</v>
       </c>
       <c r="P3" t="n">
-        <v>255.0509177074565</v>
+        <v>254.89172415804</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13631,28 +13711,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5153207665475509</v>
+        <v>0.5184171117517328</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2288411183401609</v>
+        <v>0.233424068310348</v>
       </c>
       <c r="M4" t="n">
-        <v>5.380891849492723</v>
+        <v>5.36104487864964</v>
       </c>
       <c r="N4" t="n">
-        <v>44.70922151759032</v>
+        <v>44.48904347283697</v>
       </c>
       <c r="O4" t="n">
-        <v>6.686495458578457</v>
+        <v>6.670010755076559</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6560061008905</v>
+        <v>264.6219203903944</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13709,28 +13789,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.483062859235615</v>
+        <v>0.4823523548335604</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2243939972873923</v>
+        <v>0.2264915978442595</v>
       </c>
       <c r="M5" t="n">
-        <v>5.14100913937801</v>
+        <v>5.114622361502626</v>
       </c>
       <c r="N5" t="n">
-        <v>40.29667735804318</v>
+        <v>40.05222181368298</v>
       </c>
       <c r="O5" t="n">
-        <v>6.347966395472111</v>
+        <v>6.328682470600257</v>
       </c>
       <c r="P5" t="n">
-        <v>275.4881219182326</v>
+        <v>275.495960377328</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13787,28 +13867,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4458815076789751</v>
+        <v>0.443261068377962</v>
       </c>
       <c r="J6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1464053289761236</v>
+        <v>0.1467401551348876</v>
       </c>
       <c r="M6" t="n">
-        <v>6.103240963315248</v>
+        <v>6.077191615158256</v>
       </c>
       <c r="N6" t="n">
-        <v>57.91162461899088</v>
+        <v>57.58858110958495</v>
       </c>
       <c r="O6" t="n">
-        <v>7.60996876596684</v>
+        <v>7.588714061656622</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6021347156878</v>
+        <v>267.6310225446344</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13865,28 +13945,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06344828236046397</v>
+        <v>0.06319370031474629</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006684715470486768</v>
+        <v>0.006731833538434318</v>
       </c>
       <c r="M7" t="n">
-        <v>4.411864978994238</v>
+        <v>4.38551508573346</v>
       </c>
       <c r="N7" t="n">
-        <v>29.88656118879335</v>
+        <v>29.70062494451036</v>
       </c>
       <c r="O7" t="n">
-        <v>5.466860267904544</v>
+        <v>5.44982797384563</v>
       </c>
       <c r="P7" t="n">
-        <v>329.2093852474324</v>
+        <v>329.2121910969738</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13924,7 +14004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27367,6 +27447,90 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.52961971187717,174.4603522902252</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.5303803939281,174.46036475177792</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-35.5312108338503,174.4604551219987</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-35.53211111768725,174.46085165825838</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-35.53285297306956,174.46148226312022</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-35.53305054917641,174.46254147073248</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.52961941004385,174.46032725969553</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.53038075290487,174.46034700217976</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-35.531217264148694,174.46041048443215</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-35.53211876586074,174.4608346526456</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-35.53287229912151,174.4614575686898</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-35.53305184327869,174.46253993498019</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10098,6 +10098,36 @@
         <v>330.61</v>
       </c>
       <c r="H322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>270.36</v>
+      </c>
+      <c r="C323" t="n">
+        <v>267.62</v>
+      </c>
+      <c r="D323" t="n">
+        <v>274.75</v>
+      </c>
+      <c r="E323" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="F323" t="n">
+        <v>271.41</v>
+      </c>
+      <c r="G323" t="n">
+        <v>323.83</v>
+      </c>
+      <c r="H323" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10114,7 +10144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13387,6 +13417,16 @@
       </c>
       <c r="B327" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -13555,28 +13595,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6524011035312958</v>
+        <v>0.6556688753358834</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2782591351608448</v>
+        <v>0.2815369094104875</v>
       </c>
       <c r="M2" t="n">
-        <v>6.341855331123954</v>
+        <v>6.338729389350207</v>
       </c>
       <c r="N2" t="n">
-        <v>55.64755728537668</v>
+        <v>55.54603752896033</v>
       </c>
       <c r="O2" t="n">
-        <v>7.459729035653821</v>
+        <v>7.452921409015416</v>
       </c>
       <c r="P2" t="n">
-        <v>248.1221138461284</v>
+        <v>248.085965916923</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13633,28 +13673,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5250370519273552</v>
+        <v>0.5241606229494241</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2424401573084761</v>
+        <v>0.2431929575528389</v>
       </c>
       <c r="M3" t="n">
-        <v>5.267502157235262</v>
+        <v>5.255160929131057</v>
       </c>
       <c r="N3" t="n">
-        <v>43.41873438817451</v>
+        <v>43.28902235248075</v>
       </c>
       <c r="O3" t="n">
-        <v>6.589289368981644</v>
+        <v>6.579439364602485</v>
       </c>
       <c r="P3" t="n">
-        <v>254.89172415804</v>
+        <v>254.9014191718117</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13711,28 +13751,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5184171117517328</v>
+        <v>0.5159014361385216</v>
       </c>
       <c r="J4" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L4" t="n">
-        <v>0.233424068310348</v>
+        <v>0.2328650264081471</v>
       </c>
       <c r="M4" t="n">
-        <v>5.36104487864964</v>
+        <v>5.356245665099214</v>
       </c>
       <c r="N4" t="n">
-        <v>44.48904347283697</v>
+        <v>44.3931346768977</v>
       </c>
       <c r="O4" t="n">
-        <v>6.670010755076559</v>
+        <v>6.662817322792042</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6219203903944</v>
+        <v>264.6497486689304</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13789,28 +13829,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4823523548335604</v>
+        <v>0.479184678055027</v>
       </c>
       <c r="J5" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K5" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2264915978442595</v>
+        <v>0.2252152672512218</v>
       </c>
       <c r="M5" t="n">
-        <v>5.114622361502626</v>
+        <v>5.113468275695253</v>
       </c>
       <c r="N5" t="n">
-        <v>40.05222181368298</v>
+        <v>39.99483377296361</v>
       </c>
       <c r="O5" t="n">
-        <v>6.328682470600257</v>
+        <v>6.324146881039656</v>
       </c>
       <c r="P5" t="n">
-        <v>275.495960377328</v>
+        <v>275.5310010603326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13867,28 +13907,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.443261068377962</v>
+        <v>0.4377961956483075</v>
       </c>
       <c r="J6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1467401551348876</v>
+        <v>0.1441643180768599</v>
       </c>
       <c r="M6" t="n">
-        <v>6.077191615158256</v>
+        <v>6.083047484146149</v>
       </c>
       <c r="N6" t="n">
-        <v>57.58858110958495</v>
+        <v>57.6091407324292</v>
       </c>
       <c r="O6" t="n">
-        <v>7.588714061656622</v>
+        <v>7.590068559138922</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6310225446344</v>
+        <v>267.6914746950174</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13945,28 +13985,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06319370031474629</v>
+        <v>0.05839574373611276</v>
       </c>
       <c r="J7" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K7" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006731833538434318</v>
+        <v>0.005767686088500312</v>
       </c>
       <c r="M7" t="n">
-        <v>4.38551508573346</v>
+        <v>4.393076489951101</v>
       </c>
       <c r="N7" t="n">
-        <v>29.70062494451036</v>
+        <v>29.76209306578205</v>
       </c>
       <c r="O7" t="n">
-        <v>5.44982797384563</v>
+        <v>5.455464514207938</v>
       </c>
       <c r="P7" t="n">
-        <v>329.2121910969738</v>
+        <v>329.265265854058</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14004,7 +14044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27531,6 +27571,48 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.52961883428575,174.46027951423588</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.53038317202815,174.46022738531613</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-35.53122327200394,174.46036877925349</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-35.532132801991224,174.46080344347266</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-35.53290078945378,174.46142116429823</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-35.53309571333459,174.46248787294832</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
